--- a/apps/dashboard/data/hris/payroll-exports/2026-09/SEPTEMBER 2026 DAYRATE PAYMENT SCHEDULE.xlsx
+++ b/apps/dashboard/data/hris/payroll-exports/2026-09/SEPTEMBER 2026 DAYRATE PAYMENT SCHEDULE.xlsx
@@ -4525,10 +4525,10 @@
         <v>180</v>
       </c>
       <c r="C3" s="1">
-        <v>63654567</v>
+        <v>64019738.88</v>
       </c>
       <c r="D3" s="1">
-        <v>60471838.64</v>
+        <v>60818751.92</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4557,10 +4557,10 @@
         <v>187</v>
       </c>
       <c r="C5" s="1">
-        <v>65145085.75</v>
+        <v>65510257.63</v>
       </c>
       <c r="D5" s="1">
-        <v>61887831.46</v>
+        <v>62234744.74</v>
       </c>
     </row>
   </sheetData>
@@ -5145,7 +5145,9 @@
       <c r="K7">
         <v>7</v>
       </c>
-      <c r="L7"/>
+      <c r="L7">
+        <v>1</v>
+      </c>
       <c r="M7"/>
       <c r="N7" s="1">
         <v>390000</v>
@@ -5154,7 +5156,9 @@
       <c r="P7" s="1">
         <v>25593.75</v>
       </c>
-      <c r="Q7"/>
+      <c r="Q7" s="1">
+        <v>4875</v>
+      </c>
       <c r="R7"/>
       <c r="S7" s="1">
         <v>10000</v>
@@ -5165,16 +5169,16 @@
       <c r="W7"/>
       <c r="X7"/>
       <c r="Y7" s="1">
-        <v>459718.75</v>
+        <v>464593.75</v>
       </c>
       <c r="Z7" s="1">
-        <v>22985.94</v>
+        <v>23229.69</v>
       </c>
       <c r="AA7" s="1">
-        <v>459718.75</v>
+        <v>464593.75</v>
       </c>
       <c r="AB7" s="1">
-        <v>436732.81</v>
+        <v>441364.06</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
@@ -5770,37 +5774,47 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I15"/>
-      <c r="J15"/>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>16</v>
+      </c>
       <c r="K15"/>
       <c r="L15">
         <v>13</v>
       </c>
       <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
+      <c r="N15" s="1">
+        <v>72600</v>
+      </c>
+      <c r="O15" s="1">
+        <v>54450</v>
+      </c>
       <c r="P15"/>
       <c r="Q15" s="1">
         <v>58987.5</v>
       </c>
       <c r="R15"/>
-      <c r="S15"/>
+      <c r="S15" s="1">
+        <v>2000</v>
+      </c>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
       <c r="W15"/>
       <c r="X15"/>
       <c r="Y15" s="1">
-        <v>58987.5</v>
+        <v>188037.5</v>
       </c>
       <c r="Z15" s="1">
-        <v>2949.38</v>
+        <v>9401.88</v>
       </c>
       <c r="AA15" s="1">
-        <v>58987.5</v>
+        <v>188037.5</v>
       </c>
       <c r="AB15" s="1">
-        <v>56038.12</v>
+        <v>178635.62</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
@@ -6001,9 +6015,11 @@
         </is>
       </c>
       <c r="I18">
-        <v>6</v>
-      </c>
-      <c r="J18"/>
+        <v>9</v>
+      </c>
+      <c r="J18">
+        <v>16</v>
+      </c>
       <c r="K18">
         <v>13.2</v>
       </c>
@@ -6012,9 +6028,11 @@
       </c>
       <c r="M18"/>
       <c r="N18" s="1">
-        <v>97200</v>
-      </c>
-      <c r="O18"/>
+        <v>145800</v>
+      </c>
+      <c r="O18" s="1">
+        <v>48600</v>
+      </c>
       <c r="P18" s="1">
         <v>40095</v>
       </c>
@@ -6023,7 +6041,7 @@
       </c>
       <c r="R18"/>
       <c r="S18" s="1">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="T18"/>
       <c r="U18"/>
@@ -6031,16 +6049,16 @@
       <c r="W18"/>
       <c r="X18"/>
       <c r="Y18" s="1">
-        <v>246405</v>
+        <v>345105</v>
       </c>
       <c r="Z18" s="1">
-        <v>12320.25</v>
+        <v>17255.25</v>
       </c>
       <c r="AA18" s="1">
-        <v>246405</v>
+        <v>345105</v>
       </c>
       <c r="AB18" s="1">
-        <v>234084.75</v>
+        <v>327849.75</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
@@ -6236,37 +6254,47 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I21"/>
-      <c r="J21"/>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
       <c r="K21"/>
       <c r="L21">
         <v>18</v>
       </c>
       <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
+      <c r="N21" s="1">
+        <v>16700</v>
+      </c>
+      <c r="O21" s="1">
+        <v>12525</v>
+      </c>
       <c r="P21"/>
       <c r="Q21" s="1">
         <v>75150</v>
       </c>
       <c r="R21"/>
-      <c r="S21"/>
+      <c r="S21" s="1">
+        <v>500</v>
+      </c>
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21"/>
       <c r="W21"/>
       <c r="X21"/>
       <c r="Y21" s="1">
-        <v>75150</v>
+        <v>104875</v>
       </c>
       <c r="Z21" s="1">
-        <v>3757.5</v>
+        <v>5243.75</v>
       </c>
       <c r="AA21" s="1">
-        <v>75150</v>
+        <v>104875</v>
       </c>
       <c r="AB21" s="1">
-        <v>71392.5</v>
+        <v>99631.25</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
@@ -6393,7 +6421,9 @@
       <c r="K23">
         <v>21</v>
       </c>
-      <c r="L23"/>
+      <c r="L23">
+        <v>1</v>
+      </c>
       <c r="M23"/>
       <c r="N23" s="1">
         <v>295050</v>
@@ -6402,7 +6432,9 @@
       <c r="P23" s="1">
         <v>55321.88</v>
       </c>
-      <c r="Q23"/>
+      <c r="Q23" s="1">
+        <v>3512.5</v>
+      </c>
       <c r="R23"/>
       <c r="S23" s="1">
         <v>10500</v>
@@ -6413,16 +6445,16 @@
       <c r="W23"/>
       <c r="X23"/>
       <c r="Y23" s="1">
-        <v>364384.38</v>
+        <v>367896.88</v>
       </c>
       <c r="Z23" s="1">
-        <v>18219.22</v>
+        <v>18394.84</v>
       </c>
       <c r="AA23" s="1">
-        <v>364384.38</v>
+        <v>367896.88</v>
       </c>
       <c r="AB23" s="1">
-        <v>346165.16</v>
+        <v>349502.04</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
@@ -8866,7 +8898,7 @@
         <v>21</v>
       </c>
       <c r="J54">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K54">
         <v>29</v>
@@ -8879,7 +8911,7 @@
         <v>215250</v>
       </c>
       <c r="O54" s="1">
-        <v>15375</v>
+        <v>19218.75</v>
       </c>
       <c r="P54" s="1">
         <v>55734.38</v>
@@ -8897,16 +8929,16 @@
       <c r="W54"/>
       <c r="X54"/>
       <c r="Y54" s="1">
-        <v>353234.38</v>
+        <v>357078.13</v>
       </c>
       <c r="Z54" s="1">
-        <v>17661.72</v>
+        <v>17853.91</v>
       </c>
       <c r="AA54" s="1">
-        <v>353234.38</v>
+        <v>357078.13</v>
       </c>
       <c r="AB54" s="1">
-        <v>335572.66</v>
+        <v>339224.22</v>
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
@@ -11237,7 +11269,9 @@
       <c r="K84">
         <v>10.3</v>
       </c>
-      <c r="L84"/>
+      <c r="L84">
+        <v>1</v>
+      </c>
       <c r="M84"/>
       <c r="N84" s="1">
         <v>246750</v>
@@ -11246,7 +11280,9 @@
       <c r="P84" s="1">
         <v>22692.19</v>
       </c>
-      <c r="Q84"/>
+      <c r="Q84" s="1">
+        <v>2937.5</v>
+      </c>
       <c r="R84"/>
       <c r="S84" s="1">
         <v>10500</v>
@@ -11257,16 +11293,16 @@
       <c r="W84"/>
       <c r="X84"/>
       <c r="Y84" s="1">
-        <v>300504.69</v>
+        <v>303442.19</v>
       </c>
       <c r="Z84" s="1">
-        <v>15025.23</v>
+        <v>15172.11</v>
       </c>
       <c r="AA84" s="1">
-        <v>300504.69</v>
+        <v>303442.19</v>
       </c>
       <c r="AB84" s="1">
-        <v>285479.46</v>
+        <v>288270.08</v>
       </c>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.25">
@@ -14540,7 +14576,7 @@
         <v>21</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K126">
         <v>16</v>
@@ -14553,7 +14589,7 @@
         <v>243075</v>
       </c>
       <c r="O126" s="1">
-        <v>2170.31</v>
+        <v>23873.44</v>
       </c>
       <c r="P126" s="1">
         <v>34725</v>
@@ -14571,16 +14607,16 @@
       <c r="W126"/>
       <c r="X126"/>
       <c r="Y126" s="1">
-        <v>316514.06</v>
+        <v>338217.19</v>
       </c>
       <c r="Z126" s="1">
-        <v>15825.7</v>
+        <v>16910.86</v>
       </c>
       <c r="AA126" s="1">
-        <v>316514.06</v>
+        <v>338217.19</v>
       </c>
       <c r="AB126" s="1">
-        <v>300688.36</v>
+        <v>321306.33</v>
       </c>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
@@ -14868,37 +14904,47 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I130"/>
-      <c r="J130"/>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>4</v>
+      </c>
       <c r="K130"/>
       <c r="L130">
         <v>18</v>
       </c>
       <c r="M130"/>
-      <c r="N130"/>
-      <c r="O130"/>
+      <c r="N130" s="1">
+        <v>19800</v>
+      </c>
+      <c r="O130" s="1">
+        <v>14850</v>
+      </c>
       <c r="P130"/>
       <c r="Q130" s="1">
         <v>89100</v>
       </c>
       <c r="R130"/>
-      <c r="S130"/>
+      <c r="S130" s="1">
+        <v>500</v>
+      </c>
       <c r="T130"/>
       <c r="U130"/>
       <c r="V130"/>
       <c r="W130"/>
       <c r="X130"/>
       <c r="Y130" s="1">
-        <v>89100</v>
+        <v>124250</v>
       </c>
       <c r="Z130" s="1">
-        <v>4455</v>
+        <v>6212.5</v>
       </c>
       <c r="AA130" s="1">
-        <v>89100</v>
+        <v>124250</v>
       </c>
       <c r="AB130" s="1">
-        <v>84645</v>
+        <v>118037.5</v>
       </c>
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.25">
@@ -16207,9 +16253,11 @@
         </is>
       </c>
       <c r="I147">
-        <v>1</v>
-      </c>
-      <c r="J147"/>
+        <v>2</v>
+      </c>
+      <c r="J147">
+        <v>4</v>
+      </c>
       <c r="K147">
         <v>8</v>
       </c>
@@ -16218,9 +16266,11 @@
       </c>
       <c r="M147"/>
       <c r="N147" s="1">
-        <v>20100</v>
-      </c>
-      <c r="O147"/>
+        <v>40200</v>
+      </c>
+      <c r="O147" s="1">
+        <v>15075</v>
+      </c>
       <c r="P147" s="1">
         <v>30150</v>
       </c>
@@ -16229,7 +16279,7 @@
       </c>
       <c r="R147"/>
       <c r="S147" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="T147"/>
       <c r="U147"/>
@@ -16237,16 +16287,16 @@
       <c r="W147"/>
       <c r="X147"/>
       <c r="Y147" s="1">
-        <v>181400</v>
+        <v>217075</v>
       </c>
       <c r="Z147" s="1">
-        <v>9070</v>
+        <v>10853.75</v>
       </c>
       <c r="AA147" s="1">
-        <v>181400</v>
+        <v>217075</v>
       </c>
       <c r="AB147" s="1">
-        <v>172330</v>
+        <v>206221.25</v>
       </c>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.25">
@@ -18886,11 +18936,11 @@
       </c>
       <c r="I182">
         <f>SUBTOTAL(109,Table4[Total Weekday])</f>
-        <v>3551</v>
+        <v>3561</v>
       </c>
       <c r="J182">
         <f>SUBTOTAL(109,Table4[Weekday OVT])</f>
-        <v>320.8</v>
+        <v>376.8</v>
       </c>
       <c r="K182">
         <f>SUBTOTAL(109,Table4[Total Saturday])</f>
@@ -18898,7 +18948,7 @@
       </c>
       <c r="L182">
         <f>SUBTOTAL(109,Table4[Total Sunday])</f>
-        <v>1046.4</v>
+        <v>1049.4</v>
       </c>
       <c r="M182">
         <f>SUBTOTAL(109,Table4[Night Worked])</f>
@@ -18906,11 +18956,11 @@
       </c>
       <c r="N182" s="1">
         <f>SUBTOTAL(109,Table4[Wkd Earning])</f>
-        <v>46564656</v>
+        <v>46742456</v>
       </c>
       <c r="O182" s="1">
         <f>SUBTOTAL(109,Table4[Wkd Ovt Amt])</f>
-        <v>756548.31</v>
+        <v>927595.19</v>
       </c>
       <c r="P182" s="1">
         <f>SUBTOTAL(109,Table4[Sat Ovt Amt])</f>
@@ -18918,7 +18968,7 @@
       </c>
       <c r="Q182" s="1">
         <f>SUBTOTAL(109,Table4[Sun Ovt Amt])</f>
-        <v>3139215.25</v>
+        <v>3150540.25</v>
       </c>
       <c r="R182" s="1">
         <f>SUBTOTAL(109,Table4[Night Amt])</f>
@@ -18926,7 +18976,7 @@
       </c>
       <c r="S182" s="1">
         <f>SUBTOTAL(109,Table4[Meal Allowance])</f>
-        <v>1775500</v>
+        <v>1780500</v>
       </c>
       <c r="T182" s="1">
         <f>SUBTOTAL(109,Table4[Transport])</f>
@@ -18947,19 +18997,19 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1">
         <f>SUBTOTAL(109,Table4[Total Earnings])</f>
-        <v>63654567</v>
+        <v>64019738.88</v>
       </c>
       <c r="Z182" s="1">
         <f>SUBTOTAL(109,Table4[WHT])</f>
-        <v>3182728.36</v>
+        <v>3200986.96</v>
       </c>
       <c r="AA182" s="1">
         <f>SUBTOTAL(109,Table4[Gross Amount])</f>
-        <v>63654567</v>
+        <v>64019738.88</v>
       </c>
       <c r="AB182" s="1">
         <f>SUBTOTAL(109,Table4[Amount Payable])</f>
-        <v>60471838.64</v>
+        <v>60818751.92</v>
       </c>
     </row>
   </sheetData>
@@ -19909,7 +19959,7 @@
       </c>
       <c r="F8" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>436732.81</v>
+        <v>441364.06</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20153,7 +20203,7 @@
       </c>
       <c r="F16" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>56038.12</v>
+        <v>178635.62</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20246,7 +20296,7 @@
       </c>
       <c r="F19" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>234084.75</v>
+        <v>327849.75</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20339,7 +20389,7 @@
       </c>
       <c r="F22" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>71392.5</v>
+        <v>99631.25</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -20401,7 +20451,7 @@
       </c>
       <c r="F24" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>346165.16</v>
+        <v>349502.04</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -21362,7 +21412,7 @@
       </c>
       <c r="F55" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>335572.66</v>
+        <v>339224.22</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -22288,7 +22338,7 @@
       </c>
       <c r="F85" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>285479.46</v>
+        <v>288270.08</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23578,7 +23628,7 @@
       </c>
       <c r="F127" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>300688.36</v>
+        <v>321306.33</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -23702,7 +23752,7 @@
       </c>
       <c r="F131" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>84645</v>
+        <v>118037.5</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -24229,7 +24279,7 @@
       </c>
       <c r="F148" s="16">
         <f>_xlfn.XLOOKUP(Table13[[#This Row],[Contractor Code]],DLE!A:A,DLE!AB:AB)</f>
-        <v>172330</v>
+        <v>206221.25</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -25233,7 +25283,7 @@
       <c r="E183" s="6"/>
       <c r="F183" s="5">
         <f>SUBTOTAL(109,Table13[NET Salary])</f>
-        <v>60471838.64</v>
+        <v>60818751.92</v>
       </c>
     </row>
   </sheetData>
